--- a/artfynd/A 27763-2024 artfynd.xlsx
+++ b/artfynd/A 27763-2024 artfynd.xlsx
@@ -1051,7 +1051,7 @@
         <v>136039816</v>
       </c>
       <c r="B5" t="n">
-        <v>102790</v>
+        <v>102793</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 27763-2024 artfynd.xlsx
+++ b/artfynd/A 27763-2024 artfynd.xlsx
@@ -1051,7 +1051,7 @@
         <v>136039816</v>
       </c>
       <c r="B5" t="n">
-        <v>102793</v>
+        <v>102794</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
